--- a/workers/duc-auto-chatgpt/v0.1.0/pilot-05/Duc-Auto-ChatGPT-Pilot-05.xlsx
+++ b/workers/duc-auto-chatgpt/v0.1.0/pilot-05/Duc-Auto-ChatGPT-Pilot-05.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs" sheetId="1" r:id="R24d70b4b374e45a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="2" r:id="R12f57a5fcf3a46ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs" sheetId="1" r:id="Rccea174051bb4e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="2" r:id="Rcd40cf1b26bb44af"/>
   </x:sheets>
 </x:workbook>
 </file>
